--- a/1er labo f4.xlsx
+++ b/1er labo f4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fa6626b71332f3d1/Documentos/ITBA/2026-2C/F4/TP1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="681" documentId="11_A455E61C78330EF5B78ED160A09CA3DBF0433BE0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25EB2BAA-462D-49A1-924B-5BEF997133F5}"/>
+  <xr:revisionPtr revIDLastSave="708" documentId="11_A455E61C78330EF5B78ED160A09CA3DBF0433BE0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37C5B88B-EA6B-442B-BAA8-B11E04A94234}"/>
   <bookViews>
     <workbookView xWindow="-19310" yWindow="-690" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="47">
   <si>
     <t>Mediciones</t>
   </si>
@@ -182,6 +182,21 @@
   <si>
     <t>f(e, q + delta q)</t>
   </si>
+  <si>
+    <t>e+</t>
+  </si>
+  <si>
+    <t>e-</t>
+  </si>
+  <si>
+    <t>(e+ + e-)/2</t>
+  </si>
+  <si>
+    <t>(e+ - e-)/2</t>
+  </si>
+  <si>
+    <t>f(e, q - delta q)</t>
+  </si>
 </sst>
 </file>
 
@@ -243,7 +258,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -256,8 +271,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="47">
+  <borders count="45">
     <border>
       <left/>
       <right/>
@@ -384,19 +405,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -418,19 +426,6 @@
       </right>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -848,133 +843,127 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
@@ -1462,7 +1451,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>f(e, q + delta q)</c:v>
+                  <c:v>f(e, q - delta q)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1723,7 +1712,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
@@ -2183,7 +2172,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
@@ -4299,1240 +4288,1248 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A2:R46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A2:R52"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="17.453125" customWidth="1"/>
+    <col min="2" max="2" width="17.42578125" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="15.453125" customWidth="1"/>
-    <col min="9" max="10" width="19.26953125" customWidth="1"/>
-    <col min="11" max="11" width="12.6328125" customWidth="1"/>
+    <col min="7" max="7" width="15.42578125" customWidth="1"/>
+    <col min="9" max="10" width="19.28515625" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G3" s="24" t="s">
+    <row r="2" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="G3" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="H3" s="25"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="31" t="s">
+      <c r="H3" s="69"/>
+      <c r="I3" s="70"/>
+      <c r="J3" s="74" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="32"/>
-      <c r="L3" s="55"/>
-      <c r="M3" s="38" t="s">
+      <c r="K3" s="75"/>
+      <c r="L3" s="76"/>
+      <c r="M3" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="N3" s="39"/>
-      <c r="O3" s="40"/>
-      <c r="P3" s="59"/>
-      <c r="Q3" s="21" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="79"/>
+      <c r="Q3" s="77" t="s">
         <v>36</v>
       </c>
-      <c r="R3" s="22"/>
+      <c r="R3" s="79"/>
     </row>
-    <row r="4" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="66" t="s">
+    <row r="4" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="71" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="83"/>
-      <c r="D4" s="84"/>
-      <c r="G4" s="27" t="s">
+      <c r="C4" s="72"/>
+      <c r="D4" s="73"/>
+      <c r="G4" s="16" t="s">
         <v>1</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I4" s="28" t="s">
+      <c r="I4" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="J4" s="33" t="s">
+      <c r="J4" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="K4" s="14" t="s">
+      <c r="K4" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="L4" s="20" t="s">
+      <c r="L4" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="M4" s="41" t="s">
+      <c r="M4" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="15" t="s">
+      <c r="N4" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="O4" s="42" t="s">
+      <c r="O4" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="P4" s="19"/>
-      <c r="Q4" s="12" t="s">
+      <c r="P4" s="13"/>
+      <c r="Q4" s="80" t="s">
         <v>34</v>
       </c>
-      <c r="R4" s="12" t="s">
+      <c r="R4" s="81" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="63"/>
-      <c r="B5" s="67" t="s">
+    <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="45"/>
+      <c r="B5" s="62" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="64"/>
-      <c r="D5" s="68"/>
-      <c r="G5" s="29">
+      <c r="C5" s="63"/>
+      <c r="D5" s="64"/>
+      <c r="G5" s="18">
         <v>1</v>
       </c>
       <c r="H5" s="2">
         <v>56.65</v>
       </c>
-      <c r="I5" s="30">
+      <c r="I5" s="19">
         <v>10</v>
       </c>
-      <c r="J5" s="34">
+      <c r="J5" s="21">
         <f>C16*C15/H5</f>
         <v>2.1182700794351281E-4</v>
       </c>
-      <c r="K5" s="16">
+      <c r="K5" s="12">
         <f>(9/2)*C7*J5/((C8-C9)*C13)</f>
         <v>2.1377394735475837E-9</v>
       </c>
-      <c r="L5" s="56">
+      <c r="L5" s="39">
         <f>4*C11*K5^(3/2)*(C8-C9)*C13*C12/(3*I5)</f>
         <v>1.6891994731234445E-15</v>
       </c>
-      <c r="M5" s="43">
+      <c r="M5" s="27">
         <f>ABS(C12/(H5)^2*H17)</f>
         <v>6.2320390686529223E-7</v>
       </c>
-      <c r="N5" s="23">
+      <c r="N5" s="15">
         <f>ABS(1/(2*(C17*J5)^1/2)*C17*M5)</f>
         <v>2.9420417769932335E-3</v>
       </c>
-      <c r="O5" s="44">
+      <c r="O5" s="28">
         <f>SQRT((3*L5*N5)^2/K5+(L5/I5*I17)^2)</f>
         <v>3.2245875691157835E-13</v>
       </c>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="17">
-        <f>L5-O5</f>
+      <c r="Q5" s="27">
+        <f t="shared" ref="Q5:Q16" si="0">L5-O5</f>
         <v>-3.2076955743845493E-13</v>
       </c>
-      <c r="R5" s="17">
-        <f>L5+O5</f>
+      <c r="R5" s="82">
+        <f t="shared" ref="R5:R16" si="1">L5+O5</f>
         <v>3.2414795638470177E-13</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="27" t="s">
+    <row r="6" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="16" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="28" t="s">
+      <c r="D6" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="29">
+      <c r="G6" s="18">
         <v>2</v>
       </c>
       <c r="H6" s="2">
         <v>69.13</v>
       </c>
-      <c r="I6" s="30">
+      <c r="I6" s="19">
         <v>109</v>
       </c>
-      <c r="J6" s="34">
+      <c r="J6" s="21">
         <f>C16*C15/H6</f>
         <v>1.7358599739621006E-4</v>
       </c>
-      <c r="K6" s="16">
+      <c r="K6" s="12">
         <f>(9/2)*C7*J6/((C8-C9)*C13)</f>
         <v>1.7518145693110171E-9</v>
       </c>
-      <c r="L6" s="57">
+      <c r="L6" s="40">
         <f>4*C11*K6^(3/2)*(C8-C9)*C13*C12/(3*I6)</f>
         <v>1.1496204359543101E-16</v>
       </c>
-      <c r="M6" s="43">
+      <c r="M6" s="27">
         <f>ABS(C12/(H6)^2*H17)</f>
         <v>4.1850136794495899E-7</v>
       </c>
-      <c r="N6" s="23">
+      <c r="N6" s="15">
         <f>ABS(1/(2*(C17*J6)^1/2)*C17*M6)</f>
         <v>2.410916630502918E-3</v>
       </c>
-      <c r="O6" s="44">
+      <c r="O6" s="28">
         <f>SQRT((3*L6*N6)^2/K6+(L6/I6*I17)^2)</f>
         <v>1.9866156908566924E-14</v>
       </c>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="17">
-        <f>L6-O6</f>
+      <c r="Q6" s="27">
+        <f t="shared" si="0"/>
         <v>-1.9751194864971493E-14</v>
       </c>
-      <c r="R6" s="17">
-        <f>L6+O6</f>
+      <c r="R6" s="82">
+        <f t="shared" si="1"/>
         <v>1.9981118952162355E-14</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="69" t="s">
+    <row r="7" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="46" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="3">
         <f>1.83*10^-5</f>
         <v>1.8300000000000001E-5</v>
       </c>
-      <c r="D7" s="70" t="s">
+      <c r="D7" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="G7" s="29">
+      <c r="G7" s="18">
         <v>3</v>
       </c>
       <c r="H7" s="2">
         <v>28</v>
       </c>
-      <c r="I7" s="30">
+      <c r="I7" s="19">
         <v>61</v>
       </c>
-      <c r="J7" s="34">
+      <c r="J7" s="21">
         <f>C16*C15/H7</f>
         <v>4.285714285714286E-4</v>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="12">
         <f>(9/2)*C7*J7/((C8-C9)*C13)</f>
         <v>4.3251050420168074E-9</v>
       </c>
-      <c r="L7" s="57">
+      <c r="L7" s="40">
         <f>4*C11*K7^(3/2)*(C8-C9)*C13*C12/(3*I7)</f>
         <v>7.9691853253624284E-16</v>
       </c>
-      <c r="M7" s="43">
+      <c r="M7" s="27">
         <f>ABS(C12/(H7)^2*H17)</f>
         <v>2.5510204081632657E-6</v>
       </c>
-      <c r="N7" s="23">
+      <c r="N7" s="15">
         <f>ABS(1/(2*(C17*J7)^1/2)*C17*M7)</f>
         <v>5.9523809523809538E-3</v>
       </c>
-      <c r="O7" s="44">
+      <c r="O7" s="28">
         <f>SQRT((3*L7*N7)^2/K7+(L7/I7*I17)^2)</f>
         <v>2.1638521183237024E-13</v>
       </c>
-      <c r="P7" s="5"/>
-      <c r="Q7" s="17">
-        <f>L7-O7</f>
+      <c r="Q7" s="27">
+        <f t="shared" si="0"/>
         <v>-2.1558829329983401E-13</v>
       </c>
-      <c r="R7" s="17">
-        <f>L7+O7</f>
+      <c r="R7" s="82">
+        <f t="shared" si="1"/>
         <v>2.1718213036490648E-13</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="29" t="s">
+    <row r="8" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="18" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="2">
         <v>0.81699999999999995</v>
       </c>
-      <c r="D8" s="71" t="s">
+      <c r="D8" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="29">
+      <c r="G8" s="18">
         <v>4</v>
       </c>
       <c r="H8" s="2">
         <v>114.75</v>
       </c>
-      <c r="I8" s="30">
+      <c r="I8" s="19">
         <v>5</v>
       </c>
-      <c r="J8" s="34">
+      <c r="J8" s="21">
         <f>C16*C15/H8</f>
         <v>1.0457516339869282E-4</v>
       </c>
-      <c r="K8" s="16">
+      <c r="K8" s="12">
         <f>(9/2)*C7*J8/((C8-C9)*C13)</f>
         <v>1.0553633217993082E-9</v>
       </c>
-      <c r="L8" s="57">
+      <c r="L8" s="40">
         <f>4*C11*K8^(3/2)*(C8-C9)*C13*C12/(3*I8)</f>
         <v>1.1718762777569767E-15</v>
       </c>
-      <c r="M8" s="43">
+      <c r="M8" s="27">
         <f>ABS(C12/(H8)^2*H17)</f>
         <v>1.5188839999810141E-7</v>
       </c>
-      <c r="N8" s="23">
+      <c r="N8" s="15">
         <f>ABS(1/(2*(C17*J8)^1/2)*C17*M8)</f>
         <v>1.4524328249818448E-3</v>
       </c>
-      <c r="O8" s="44">
+      <c r="O8" s="28">
         <f>SQRT((3*L8*N8)^2/K8+(L8/I8*I17)^2)</f>
         <v>1.5718185870231393E-13</v>
       </c>
-      <c r="P8" s="5"/>
-      <c r="Q8" s="17">
-        <f>L8-O8</f>
+      <c r="Q8" s="27">
+        <f t="shared" si="0"/>
         <v>-1.5600998242455696E-13</v>
       </c>
-      <c r="R8" s="17">
-        <f>L8+O8</f>
+      <c r="R8" s="82">
+        <f t="shared" si="1"/>
         <v>1.5835373498007089E-13</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="29" t="s">
+    <row r="9" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="18" t="s">
         <v>11</v>
       </c>
       <c r="C9" s="2">
         <v>1E-3</v>
       </c>
-      <c r="D9" s="71" t="s">
+      <c r="D9" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="G9" s="29">
+      <c r="G9" s="18">
         <v>5</v>
       </c>
       <c r="H9" s="2">
         <v>6.4</v>
       </c>
-      <c r="I9" s="30">
+      <c r="I9" s="19">
         <v>50</v>
       </c>
-      <c r="J9" s="34">
+      <c r="J9" s="21">
         <f>C16*C15/H9</f>
         <v>1.8749999999999999E-3</v>
       </c>
-      <c r="K9" s="16">
+      <c r="K9" s="12">
         <f>(9/2)*C7*J9/((C8-C9)*C13)</f>
         <v>1.8922334558823531E-8</v>
       </c>
-      <c r="L9" s="57">
+      <c r="L9" s="40">
         <f>4*C11*K9^(3/2)*(C8-C9)*C13*C12/(3*I9)</f>
         <v>8.8969437189529275E-15</v>
       </c>
-      <c r="M9" s="43">
+      <c r="M9" s="27">
         <f>ABS(C12/(H9)^2*H17)</f>
         <v>4.8828124999999989E-5</v>
       </c>
-      <c r="N9" s="23">
+      <c r="N9" s="15">
         <f>ABS(1/(2*(C17*J9)^1/2)*C17*M9)</f>
         <v>2.6041666666666664E-2</v>
       </c>
-      <c r="O9" s="44">
+      <c r="O9" s="28">
         <f>SQRT((3*L9*N9)^2/K9+(L9/I9*I17)^2)</f>
         <v>5.0529327434931399E-12</v>
       </c>
-      <c r="P9" s="5"/>
-      <c r="Q9" s="17">
-        <f>L9-O9</f>
+      <c r="Q9" s="27">
+        <f t="shared" si="0"/>
         <v>-5.0440357997741873E-12</v>
       </c>
-      <c r="R9" s="17">
-        <f>L9+O9</f>
+      <c r="R9" s="82">
+        <f t="shared" si="1"/>
         <v>5.0618296872120925E-12</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="72" t="s">
+    <row r="10" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="49" t="s">
         <v>23</v>
       </c>
       <c r="C10" s="2">
         <f>1.602*10^-19</f>
         <v>1.602E-19</v>
       </c>
-      <c r="D10" s="73" t="s">
+      <c r="D10" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="G10" s="29">
+      <c r="G10" s="18">
         <v>6</v>
       </c>
       <c r="H10" s="2">
         <v>28.7</v>
       </c>
-      <c r="I10" s="30">
+      <c r="I10" s="19">
         <v>79</v>
       </c>
-      <c r="J10" s="35">
+      <c r="J10" s="22">
         <f>C16*C15/H10</f>
         <v>4.181184668989547E-4</v>
       </c>
-      <c r="K10" s="16">
+      <c r="K10" s="12">
         <f>(9/2)*C7*J10/((C8-C9)*C13)</f>
         <v>4.2196146751383483E-9</v>
       </c>
-      <c r="L10" s="57">
+      <c r="L10" s="40">
         <f>4*C11*K10^(3/2)*(C8-C9)*C13*C12/(3*I10)</f>
         <v>5.9296747468948444E-16</v>
       </c>
-      <c r="M10" s="43">
+      <c r="M10" s="27">
         <f>ABS(C12/(H10)^2*H17)</f>
         <v>2.4280979494712821E-6</v>
       </c>
-      <c r="N10" s="23">
+      <c r="N10" s="15">
         <f>ABS(1/(2*(C17*J10)^1/2)*C17*M10)</f>
         <v>5.8072009291521504E-3</v>
       </c>
-      <c r="O10" s="44">
+      <c r="O10" s="28">
         <f>SQRT((3*L10*N10)^2/K10+(L10/I10*I17)^2)</f>
         <v>1.5903129195344042E-13</v>
       </c>
-      <c r="P10" s="5"/>
-      <c r="Q10" s="17">
-        <f>L10-O10</f>
+      <c r="Q10" s="27">
+        <f t="shared" si="0"/>
         <v>-1.5843832447875093E-13</v>
       </c>
-      <c r="R10" s="17">
-        <f>L10+O10</f>
+      <c r="R10" s="82">
+        <f t="shared" si="1"/>
         <v>1.5962425942812991E-13</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="72" t="s">
+    <row r="11" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="49" t="s">
         <v>19</v>
       </c>
       <c r="C11" s="2">
         <v>3.1415926535900001</v>
       </c>
-      <c r="D11" s="73" t="s">
+      <c r="D11" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="G11" s="29">
+      <c r="G11" s="18">
         <v>7</v>
       </c>
       <c r="H11" s="2">
         <v>39.659999999999997</v>
       </c>
-      <c r="I11" s="30">
+      <c r="I11" s="19">
         <v>173</v>
       </c>
-      <c r="J11" s="34">
+      <c r="J11" s="21">
         <f>C16*C15/H11</f>
         <v>3.0257186081694405E-4</v>
       </c>
-      <c r="K11" s="16">
+      <c r="K11" s="12">
         <f>(9/2)*C7*J11/((C8-C9)*C13)</f>
         <v>3.0535285218474689E-9</v>
       </c>
-      <c r="L11" s="57">
+      <c r="L11" s="40">
         <f>4*C11*K11^(3/2)*(C8-C9)*C13*C12/(3*I11)</f>
         <v>1.6668850084116009E-16</v>
       </c>
-      <c r="M11" s="43">
+      <c r="M11" s="27">
         <f>ABS(C12/(H11)^2*H17)</f>
         <v>1.2715240410865023E-6</v>
       </c>
-      <c r="N11" s="23">
+      <c r="N11" s="15">
         <f>ABS(1/(2*(C17*J11)^1/2)*C17*M11)</f>
         <v>4.2023869557908898E-3</v>
       </c>
-      <c r="O11" s="44">
+      <c r="O11" s="28">
         <f>SQRT((3*L11*N11)^2/K11+(L11/I11*I17)^2)</f>
         <v>3.8029616501197478E-14</v>
       </c>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="17">
-        <f>L11-O11</f>
+      <c r="Q11" s="27">
+        <f t="shared" si="0"/>
         <v>-3.7862928000356318E-14</v>
       </c>
-      <c r="R11" s="17">
-        <f>L11+O11</f>
+      <c r="R11" s="82">
+        <f t="shared" si="1"/>
         <v>3.8196305002038638E-14</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="29" t="s">
+    <row r="12" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="18" t="s">
         <v>12</v>
       </c>
       <c r="C12" s="4">
         <f>5*10^-3</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="D12" s="73" t="s">
+      <c r="D12" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="G12" s="29">
+      <c r="G12" s="18">
         <v>8</v>
       </c>
       <c r="H12" s="2">
         <v>10.6</v>
       </c>
-      <c r="I12" s="30">
+      <c r="I12" s="19">
         <v>53</v>
       </c>
-      <c r="J12" s="34">
+      <c r="J12" s="21">
         <f>C16*C15/H12</f>
         <v>1.1320754716981133E-3</v>
       </c>
-      <c r="K12" s="16">
+      <c r="K12" s="12">
         <f>(9/2)*C7*J12/((C8-C9)*C13)</f>
         <v>1.142480577136515E-8</v>
       </c>
-      <c r="L12" s="57">
+      <c r="L12" s="40">
         <f>4*C11*K12^(3/2)*(C8-C9)*C13*C12/(3*I12)</f>
         <v>3.9377318743614343E-15</v>
       </c>
-      <c r="M12" s="43">
+      <c r="M12" s="27">
         <f>ABS(C12/(H12)^2*H17)</f>
         <v>1.7799928800284801E-5</v>
       </c>
-      <c r="N12" s="23">
+      <c r="N12" s="15">
         <f>ABS(1/(2*(C17*J12)^1/2)*C17*M12)</f>
         <v>1.5723270440251576E-2</v>
       </c>
-      <c r="O12" s="44">
+      <c r="O12" s="28">
         <f>SQRT((3*L12*N12)^2/K12+(L12/I12*I17)^2)</f>
         <v>1.7377442932840547E-12</v>
       </c>
-      <c r="P12" s="5"/>
-      <c r="Q12" s="17">
-        <f>L12-O12</f>
+      <c r="Q12" s="27">
+        <f t="shared" si="0"/>
         <v>-1.7338065614096932E-12</v>
       </c>
-      <c r="R12" s="17">
-        <f>L12+O12</f>
+      <c r="R12" s="82">
+        <f t="shared" si="1"/>
         <v>1.7416820251584161E-12</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="29" t="s">
+    <row r="13" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="18" t="s">
         <v>13</v>
       </c>
       <c r="C13" s="4">
         <v>10</v>
       </c>
-      <c r="D13" s="73" t="s">
+      <c r="D13" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="G13" s="29">
+      <c r="G13" s="18">
         <v>9</v>
       </c>
       <c r="H13" s="2">
         <v>10.28</v>
       </c>
-      <c r="I13" s="30">
+      <c r="I13" s="19">
         <v>56</v>
       </c>
-      <c r="J13" s="34">
+      <c r="J13" s="21">
         <f>C16*C15/H13</f>
         <v>1.1673151750972765E-3</v>
       </c>
-      <c r="K13" s="16">
+      <c r="K13" s="12">
         <f>(9/2)*C7*J13/((C8-C9)*C13)</f>
         <v>1.1780441748683912E-8</v>
       </c>
-      <c r="L13" s="57">
+      <c r="L13" s="40">
         <f>4*C11*K13^(3/2)*(C8-C9)*C13*C12/(3*I13)</f>
         <v>3.9021423608125531E-15</v>
       </c>
-      <c r="M13" s="43">
+      <c r="M13" s="27">
         <f>ABS(C12/(H13)^2*H17)</f>
         <v>1.8925343305727571E-5</v>
       </c>
-      <c r="N13" s="23">
+      <c r="N13" s="15">
         <f>ABS(1/(2*(C17*J13)^1/2)*C17*M13)</f>
         <v>1.621271076523995E-2</v>
       </c>
-      <c r="O13" s="44">
+      <c r="O13" s="28">
         <f>SQRT((3*L13*N13)^2/K13+(L13/I13*I17)^2)</f>
         <v>1.7486351912419393E-12</v>
       </c>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="17">
-        <f>L13-O13</f>
+      <c r="Q13" s="27">
+        <f t="shared" si="0"/>
         <v>-1.7447330488811267E-12</v>
       </c>
-      <c r="R13" s="17">
-        <f>L13+O13</f>
+      <c r="R13" s="82">
+        <f t="shared" si="1"/>
         <v>1.7525373336027519E-12</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="74" t="s">
+    <row r="14" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="65" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="65"/>
-      <c r="D14" s="75"/>
-      <c r="G14" s="29">
+      <c r="C14" s="66"/>
+      <c r="D14" s="67"/>
+      <c r="G14" s="18">
         <v>10</v>
       </c>
       <c r="H14" s="2">
         <v>6.9</v>
       </c>
-      <c r="I14" s="30">
+      <c r="I14" s="19">
         <v>38</v>
       </c>
-      <c r="J14" s="34">
+      <c r="J14" s="21">
         <f>C16*C15/H14</f>
         <v>1.7391304347826085E-3</v>
       </c>
-      <c r="K14" s="16">
+      <c r="K14" s="12">
         <f>(9/2)*C7*J14/((C8-C9)*C13)</f>
         <v>1.7551150895140664E-8</v>
       </c>
-      <c r="L14" s="57">
+      <c r="L14" s="40">
         <f>4*C11*K14^(3/2)*(C8-C9)*C13*C12/(3*I14)</f>
         <v>1.0457396522590743E-14</v>
       </c>
-      <c r="M14" s="43">
+      <c r="M14" s="27">
         <f>ABS(C12/(H14)^2*H17)</f>
         <v>4.2007981516488134E-5</v>
       </c>
-      <c r="N14" s="23">
+      <c r="N14" s="15">
         <f>ABS(1/(2*(C17*J14)^1/2)*C17*M14)</f>
         <v>2.4154589371980676E-2</v>
       </c>
-      <c r="O14" s="44">
+      <c r="O14" s="28">
         <f>SQRT((3*L14*N14)^2/K14+(L14/I14*I17)^2)</f>
         <v>5.7199429071272475E-12</v>
       </c>
-      <c r="P14" s="5"/>
-      <c r="Q14" s="17">
-        <f>L14-O14</f>
+      <c r="Q14" s="27">
+        <f t="shared" si="0"/>
         <v>-5.7094855106046566E-12</v>
       </c>
-      <c r="R14" s="17">
-        <f>L14+O14</f>
+      <c r="R14" s="82">
+        <f t="shared" si="1"/>
         <v>5.7304003036498384E-12</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="76" t="s">
+    <row r="15" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="6">
         <v>6</v>
       </c>
-      <c r="D15" s="77" t="s">
+      <c r="D15" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="G15" s="29">
+      <c r="G15" s="18">
         <v>11</v>
       </c>
       <c r="H15" s="2">
         <v>14.67</v>
       </c>
-      <c r="I15" s="30">
+      <c r="I15" s="19">
         <v>61</v>
       </c>
-      <c r="J15" s="34">
+      <c r="J15" s="21">
         <f>C16*C15/H15</f>
         <v>8.1799591002044991E-4</v>
       </c>
-      <c r="K15" s="16">
+      <c r="K15" s="12">
         <f>(9/2)*C7*J15/((C8-C9)*C13)</f>
         <v>8.2551425478166734E-9</v>
       </c>
-      <c r="L15" s="57">
+      <c r="L15" s="40">
         <f>4*C11*K15^(3/2)*(C8-C9)*C13*C12/(3*I15)</f>
         <v>2.1013858464789083E-15</v>
       </c>
-      <c r="M15" s="43">
+      <c r="M15" s="27">
         <f>ABS(C12/(H15)^2*H17)</f>
         <v>9.2932959556970008E-6</v>
       </c>
-      <c r="N15" s="23">
+      <c r="N15" s="15">
         <f>ABS(1/(2*(C17*J15)^1/2)*C17*M15)</f>
         <v>1.1361054305839585E-2</v>
       </c>
-      <c r="O15" s="44">
+      <c r="O15" s="28">
         <f>SQRT((3*L15*N15)^2/K15+(L15/I15*I17)^2)</f>
         <v>7.8828526493005111E-13</v>
       </c>
-      <c r="P15" s="5"/>
-      <c r="Q15" s="17">
-        <f>L15-O15</f>
+      <c r="Q15" s="27">
+        <f t="shared" si="0"/>
         <v>-7.8618387908357218E-13</v>
       </c>
-      <c r="R15" s="17">
-        <f>L15+O15</f>
+      <c r="R15" s="82">
+        <f t="shared" si="1"/>
         <v>7.9038665077653005E-13</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="78" t="s">
+    <row r="16" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="9">
+      <c r="C16" s="7">
         <f>2*10^-3</f>
         <v>2E-3</v>
       </c>
-      <c r="D16" s="79" t="s">
+      <c r="D16" s="54" t="s">
         <v>16</v>
       </c>
-      <c r="G16" s="29">
+      <c r="G16" s="18">
         <v>12</v>
       </c>
       <c r="H16" s="2">
         <v>3.67</v>
       </c>
-      <c r="I16" s="30">
+      <c r="I16" s="19">
         <v>49</v>
       </c>
-      <c r="J16" s="36">
+      <c r="J16" s="23">
         <f>C16*C15/H16</f>
         <v>3.2697547683923707E-3</v>
       </c>
-      <c r="K16" s="37">
+      <c r="K16" s="24">
         <f>(9/2)*C7*J16/((C8-C9)*C13)</f>
         <v>3.2998076614842125E-8</v>
       </c>
-      <c r="L16" s="58">
+      <c r="L16" s="41">
         <f>4*C11*K16^(3/2)*(C8-C9)*C13*C12/(3*I16)</f>
         <v>2.090670697035501E-14</v>
       </c>
-      <c r="M16" s="45">
+      <c r="M16" s="29">
         <f>ABS(C12/(H16)^2*H17)</f>
         <v>1.4849022563089787E-4</v>
       </c>
-      <c r="N16" s="46">
+      <c r="N16" s="30">
         <f>ABS(1/(2*(C17*J16)^1/2)*C17*M16)</f>
         <v>4.5413260672116255E-2</v>
       </c>
-      <c r="O16" s="47">
+      <c r="O16" s="31">
         <f>SQRT((3*L16*N16)^2/K16+(L16/I16*I17)^2)</f>
         <v>1.5679971191996246E-11</v>
       </c>
-      <c r="P16" s="5"/>
-      <c r="Q16" s="18">
-        <f>L16-O16</f>
+      <c r="Q16" s="29">
+        <f t="shared" si="0"/>
         <v>-1.5659064485025892E-11</v>
       </c>
-      <c r="R16" s="18">
-        <f>L16+O16</f>
+      <c r="R16" s="83">
+        <f t="shared" si="1"/>
         <v>1.57008778989666E-11</v>
       </c>
     </row>
-    <row r="17" spans="2:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="80" t="s">
+    <row r="17" spans="2:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="55" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="81">
+      <c r="C17" s="56">
         <f>9/2*C7/((C8-C9)*C13)</f>
         <v>1.0091911764705884E-5</v>
       </c>
-      <c r="D17" s="82" t="s">
+      <c r="D17" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="F17" s="48" t="s">
+      <c r="F17" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="G17" s="49"/>
-      <c r="H17" s="50">
+      <c r="G17" s="33"/>
+      <c r="H17" s="34">
         <v>0.4</v>
       </c>
-      <c r="I17" s="51">
+      <c r="I17" s="35">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="5"/>
+    <row r="18" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
     </row>
-    <row r="19" spans="2:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="13"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
+    <row r="19" spans="2:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="5"/>
     </row>
-    <row r="20" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="13"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="G20" s="52" t="s">
+    <row r="20" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="5"/>
+      <c r="G20" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="H20" s="60" t="s">
+      <c r="H20" s="42" t="s">
         <v>37</v>
       </c>
-      <c r="I20" s="60" t="s">
+      <c r="I20" s="42" t="s">
+        <v>46</v>
+      </c>
+      <c r="J20" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="J20" s="85" t="s">
-        <v>41</v>
-      </c>
     </row>
-    <row r="21" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="13"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="G21" s="53">
+    <row r="21" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="5"/>
+      <c r="G21" s="37">
         <f>(1+0*0.7/15)*10^-19</f>
         <v>9.9999999999999998E-20</v>
       </c>
-      <c r="H21" s="11" cm="1">
+      <c r="H21" s="9" cm="1">
         <f t="array" ref="H21">ABS(SUMPRODUCT((L5:L16/G21-ROUND(L5:L16/G21+0.5,0))^2))</f>
         <v>2.9828649390387598</v>
       </c>
-      <c r="I21" s="10" cm="1">
+      <c r="I21" s="8" cm="1">
         <f t="array" ref="I21">ABS(SUMPRODUCT((Q5:Q16/G21-ROUND(Q5:Q16/G21+0.5,0))^2))</f>
         <v>5.8891910636335227</v>
       </c>
-      <c r="J21" s="61" cm="1">
+      <c r="J21" s="43" cm="1">
         <f t="array" ref="J21">ABS(SUMPRODUCT((R5:R16/G21-ROUND(R5:R16/G21+0.5,0))^2))</f>
         <v>5.0099132363340342</v>
       </c>
     </row>
-    <row r="22" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="6"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="G22" s="53">
+    <row r="22" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="5"/>
+      <c r="G22" s="37">
         <f>(1+1*0.7/25)*10^-19</f>
         <v>1.0279999999999999E-19</v>
       </c>
-      <c r="H22" s="11" cm="1">
+      <c r="H22" s="9" cm="1">
         <f t="array" ref="H22">ABS(SUMPRODUCT((L5:L16/G22-ROUND(L5:L16/G22+0.5,0))^2))</f>
         <v>3.857477652835466</v>
       </c>
-      <c r="I22" s="11" cm="1">
+      <c r="I22" s="9" cm="1">
         <f t="array" ref="I22">ABS(SUMPRODUCT((Q5:Q16/G22-ROUND(Q5:Q16/G22+0.5,0))^2))</f>
         <v>2.5706934594151596</v>
       </c>
-      <c r="J22" s="44" cm="1">
+      <c r="J22" s="28" cm="1">
         <f t="array" ref="J22">ABS(SUMPRODUCT((R5:R16/G22-ROUND(R5:R16/G22+0.5,0))^2))</f>
         <v>4.5751732367377489</v>
       </c>
     </row>
-    <row r="23" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="G23" s="53">
+    <row r="23" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G23" s="37">
         <f>(1+2*0.7/25)*10^-19</f>
         <v>1.056E-19</v>
       </c>
-      <c r="H23" s="11" cm="1">
+      <c r="H23" s="9" cm="1">
         <f t="array" ref="H23">ABS(SUMPRODUCT((L5:L16/G23-ROUND(L5:L16/G23+0.5,0))^2))</f>
         <v>5.5574422691643948</v>
       </c>
-      <c r="I23" s="11" cm="1">
+      <c r="I23" s="9" cm="1">
         <f t="array" ref="I23">ABS(SUMPRODUCT((Q5:Q16/G23-ROUND(Q5:Q16/G23+0.5,0))^2))</f>
         <v>4.2866694226677016</v>
       </c>
-      <c r="J23" s="44" cm="1">
+      <c r="J23" s="28" cm="1">
         <f t="array" ref="J23">ABS(SUMPRODUCT((R5:R16/G23-ROUND(R5:R16/G23+0.5,0))^2))</f>
         <v>3.5686965786924887</v>
       </c>
     </row>
-    <row r="24" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="G24" s="53">
+    <row r="24" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G24" s="37">
         <f>(1+3*0.7/25)*10^-19</f>
         <v>1.084E-19</v>
       </c>
-      <c r="H24" s="11" cm="1">
+      <c r="H24" s="9" cm="1">
         <f t="array" ref="H24">ABS(SUMPRODUCT((L5:L16/G24-ROUND(L5:L16/G24+0.5,0))^2))</f>
         <v>4.1382461471802863</v>
       </c>
-      <c r="I24" s="11" cm="1">
+      <c r="I24" s="9" cm="1">
         <f t="array" ref="I24">ABS(SUMPRODUCT((Q5:Q16/G24-ROUND(Q5:Q16/G24+0.5,0))^2))</f>
         <v>3.7830653839124646</v>
       </c>
-      <c r="J24" s="44" cm="1">
+      <c r="J24" s="28" cm="1">
         <f t="array" ref="J24">ABS(SUMPRODUCT((R5:R16/G24-ROUND(R5:R16/G24+0.5,0))^2))</f>
         <v>3.3200731454119161</v>
       </c>
     </row>
-    <row r="25" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G25" s="53">
+    <row r="25" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G25" s="37">
         <f>(1+4*0.7/25)*10^-19</f>
         <v>1.1120000000000001E-19</v>
       </c>
-      <c r="H25" s="11" cm="1">
+      <c r="H25" s="9" cm="1">
         <f t="array" ref="H25">ABS(SUMPRODUCT((L5:L16/G25-ROUND(L5:L16/G25+0.5,0))^2))</f>
         <v>3.2828762285659914</v>
       </c>
-      <c r="I25" s="11" cm="1">
+      <c r="I25" s="9" cm="1">
         <f t="array" ref="I25">ABS(SUMPRODUCT((Q5:Q16/G25-ROUND(Q5:Q16/G25+0.5,0))^2))</f>
         <v>3.584729204333581</v>
       </c>
-      <c r="J25" s="44" cm="1">
+      <c r="J25" s="28" cm="1">
         <f t="array" ref="J25">ABS(SUMPRODUCT((R5:R16/G25-ROUND(R5:R16/G25+0.5,0))^2))</f>
         <v>3.5114849546254194</v>
       </c>
     </row>
-    <row r="26" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G26" s="53">
+    <row r="26" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G26" s="37">
         <f>(1+5*0.7/25)*10^-19</f>
         <v>1.14E-19</v>
       </c>
-      <c r="H26" s="11" cm="1">
+      <c r="H26" s="9" cm="1">
         <f t="array" ref="H26">ABS(SUMPRODUCT((L5:L16/G26-ROUND(L5:L16/G26+0.5,0))^2))</f>
         <v>4.4978354407077097</v>
       </c>
-      <c r="I26" s="11" cm="1">
+      <c r="I26" s="9" cm="1">
         <f t="array" ref="I26">ABS(SUMPRODUCT((Q5:Q16/G26-ROUND(Q5:Q16/G26+0.5,0))^2))</f>
         <v>4.5052614288174135</v>
       </c>
-      <c r="J26" s="44" cm="1">
+      <c r="J26" s="28" cm="1">
         <f t="array" ref="J26">ABS(SUMPRODUCT((R5:R16/G26-ROUND(R5:R16/G26+0.5,0))^2))</f>
         <v>4.0106787280183136</v>
       </c>
     </row>
-    <row r="27" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G27" s="53">
+    <row r="27" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G27" s="37">
         <f>(1+6*0.7/25)*10^-19</f>
         <v>1.168E-19</v>
       </c>
-      <c r="H27" s="11" cm="1">
+      <c r="H27" s="9" cm="1">
         <f t="array" ref="H27">SUMPRODUCT((L5:L16/G27-ROUND(L5:L16/G27+0.5,0))^2)</f>
         <v>3.8779843369651021</v>
       </c>
-      <c r="I27" s="11" cm="1">
+      <c r="I27" s="9" cm="1">
         <f t="array" ref="I27">ABS(SUMPRODUCT((Q5:Q16/G27-ROUND(Q5:Q16/G27+0.5,0))^2))</f>
         <v>5.0359956446459631</v>
       </c>
-      <c r="J27" s="44" cm="1">
+      <c r="J27" s="28" cm="1">
         <f t="array" ref="J27">ABS(SUMPRODUCT((R5:R16/G27-ROUND(R5:R16/G27+0.5,0))^2))</f>
         <v>5.615122094274084</v>
       </c>
     </row>
-    <row r="28" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G28" s="53">
+    <row r="28" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G28" s="37">
         <f>(1+7*0.7/25)*10^-19</f>
         <v>1.196E-19</v>
       </c>
-      <c r="H28" s="11" cm="1">
+      <c r="H28" s="9" cm="1">
         <f t="array" ref="H28">ABS(SUMPRODUCT((L5:L16/G28-ROUND(L5:L16/G28+0.5,0))^2))</f>
         <v>5.1125539223378391</v>
       </c>
-      <c r="I28" s="11" cm="1">
+      <c r="I28" s="9" cm="1">
         <f t="array" ref="I28">ABS(SUMPRODUCT((Q5:Q16/G28-ROUND(Q5:Q16/G28+0.5,0))^2))</f>
         <v>4.7138100397172664</v>
       </c>
-      <c r="J28" s="44" cm="1">
+      <c r="J28" s="28" cm="1">
         <f t="array" ref="J28">ABS(SUMPRODUCT((R5:R16/G28-ROUND(R5:R16/G28+0.5,0))^2))</f>
         <v>6.1085964175383509</v>
       </c>
     </row>
-    <row r="29" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G29" s="53">
+    <row r="29" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G29" s="37">
         <f>(1+8*0.7/25)*10^-19</f>
         <v>1.2239999999999999E-19</v>
       </c>
-      <c r="H29" s="11" cm="1">
+      <c r="H29" s="9" cm="1">
         <f t="array" ref="H29">ABS(SUMPRODUCT((L5:L16/G29-ROUND(L5:L16/G29+0.5,0))^2))</f>
         <v>5.1576563326390632</v>
       </c>
-      <c r="I29" s="11" cm="1">
+      <c r="I29" s="9" cm="1">
         <f t="array" ref="I29">ABS(SUMPRODUCT((Q5:Q16/G29-ROUND(Q5:Q16/G29+0.5,0))^2))</f>
         <v>5.0882608701331478</v>
       </c>
-      <c r="J29" s="44" cm="1">
+      <c r="J29" s="28" cm="1">
         <f t="array" ref="J29">ABS(SUMPRODUCT((R5:R16/G29-ROUND(R5:R16/G29+0.5,0))^2))</f>
         <v>3.0913194229237098</v>
       </c>
     </row>
-    <row r="30" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G30" s="53">
+    <row r="30" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G30" s="37">
         <f>(1+9*0.7/25)*10^-19</f>
         <v>1.2519999999999999E-19</v>
       </c>
-      <c r="H30" s="11" cm="1">
+      <c r="H30" s="9" cm="1">
         <f t="array" ref="H30">ABS(SUMPRODUCT((L5:L16/G30-ROUND(L5:L16/G30+0.5,0))^2))</f>
         <v>6.1558214527243891</v>
       </c>
-      <c r="I30" s="11" cm="1">
+      <c r="I30" s="9" cm="1">
         <f t="array" ref="I30">ABS(SUMPRODUCT((Q5:Q16/G30-ROUND(Q5:Q16/G30+0.5,0))^2))</f>
         <v>3.2347659470855405</v>
       </c>
-      <c r="J30" s="44" cm="1">
+      <c r="J30" s="28" cm="1">
         <f t="array" ref="J30">ABS(SUMPRODUCT((R5:R16/G30-ROUND(R5:R16/G30+0.5,0))^2))</f>
         <v>5.1343167190943673</v>
       </c>
     </row>
-    <row r="31" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G31" s="53">
+    <row r="31" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G31" s="37">
         <f>(1+10*0.7/25)*10^-19</f>
         <v>1.2799999999999999E-19</v>
       </c>
-      <c r="H31" s="11" cm="1">
+      <c r="H31" s="9" cm="1">
         <f t="array" ref="H31">ABS(SUMPRODUCT((L5:L16/G31-ROUND(L5:L16/G31+0.5,0))^2))</f>
         <v>4.2257541504203084</v>
       </c>
-      <c r="I31" s="11" cm="1">
+      <c r="I31" s="9" cm="1">
         <f t="array" ref="I31">ABS(SUMPRODUCT((Q5:Q16/G31-ROUND(Q5:Q16/G31+0.5,0))^2))</f>
         <v>4.1620490938751109</v>
       </c>
-      <c r="J31" s="44" cm="1">
+      <c r="J31" s="28" cm="1">
         <f t="array" ref="J31">ABS(SUMPRODUCT((R5:R16/G31-ROUND(R5:R16/G31+0.5,0))^2))</f>
         <v>2.2036482276470104</v>
       </c>
     </row>
-    <row r="32" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G32" s="53">
+    <row r="32" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G32" s="61">
         <f>(1+11*0.7/25)*10^-19</f>
         <v>1.3080000000000001E-19</v>
       </c>
-      <c r="H32" s="11" cm="1">
+      <c r="H32" s="9" cm="1">
         <f t="array" ref="H32">ABS(SUMPRODUCT((L5:L16/G32-ROUND(L5:L16/G32+0.5,0))^2))</f>
         <v>3.0866308382184662</v>
       </c>
-      <c r="I32" s="11" cm="1">
+      <c r="I32" s="9" cm="1">
         <f t="array" ref="I32">ABS(SUMPRODUCT((Q5:Q16/G32-ROUND(Q5:Q16/G32+0.5,0))^2))</f>
         <v>5.104900037263306</v>
       </c>
-      <c r="J32" s="44" cm="1">
+      <c r="J32" s="59" cm="1">
         <f t="array" ref="J32">ABS(SUMPRODUCT((R5:R16/G32-ROUND(R5:R16/G32+0.5,0))^2))</f>
         <v>1.6256983087676873</v>
       </c>
     </row>
-    <row r="33" spans="7:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G33" s="53">
+    <row r="33" spans="7:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G33" s="37">
         <f>(1+12*0.7/25)*10^-19</f>
         <v>1.3359999999999998E-19</v>
       </c>
-      <c r="H33" s="11" cm="1">
+      <c r="H33" s="9" cm="1">
         <f t="array" ref="H33">ABS(SUMPRODUCT((L5:L16/G33-ROUND(L5:L16/G33+0.5,0))^2))</f>
         <v>2.5735782660836843</v>
       </c>
-      <c r="I33" s="11" cm="1">
+      <c r="I33" s="9" cm="1">
         <f t="array" ref="I33">ABS(SUMPRODUCT((Q5:Q16/G33-ROUND(Q5:Q16/G33+0.5,0))^2))</f>
         <v>4.8267297873690351</v>
       </c>
-      <c r="J33" s="44" cm="1">
+      <c r="J33" s="28" cm="1">
         <f t="array" ref="J33">ABS(SUMPRODUCT((R5:R16/G33-ROUND(R5:R16/G33+0.5,0))^2))</f>
         <v>4.2755961379165663</v>
       </c>
     </row>
-    <row r="34" spans="7:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G34" s="53">
+    <row r="34" spans="7:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G34" s="37">
         <f>(1+13*0.7/25)*10^-19</f>
         <v>1.3639999999999998E-19</v>
       </c>
-      <c r="H34" s="11" cm="1">
+      <c r="H34" s="9" cm="1">
         <f t="array" ref="H34">ABS(SUMPRODUCT((L5:L16/G34-ROUND(L5:L16/G34+0.5,0))^2))</f>
         <v>6.1901185892839825</v>
       </c>
-      <c r="I34" s="11" cm="1">
+      <c r="I34" s="9" cm="1">
         <f t="array" ref="I34">ABS(SUMPRODUCT((Q5:Q16/G34-ROUND(Q5:Q16/G34+0.5,0))^2))</f>
         <v>3.1360051566457203</v>
       </c>
-      <c r="J34" s="44" cm="1">
+      <c r="J34" s="28" cm="1">
         <f t="array" ref="J34">ABS(SUMPRODUCT((R5:R16/G34-ROUND(R5:R16/G34+0.5,0))^2))</f>
         <v>4.5718061413709057</v>
       </c>
     </row>
-    <row r="35" spans="7:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G35" s="53">
+    <row r="35" spans="7:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G35" s="37">
         <f>(1+14*0.7/25)*10^-19</f>
         <v>1.392E-19</v>
       </c>
-      <c r="H35" s="11" cm="1">
+      <c r="H35" s="9" cm="1">
         <f t="array" ref="H35">ABS(SUMPRODUCT((L5:L16/G35-ROUND(L5:L16/G35+0.5,0))^2))</f>
         <v>2.7110882675497061</v>
       </c>
-      <c r="I35" s="11" cm="1">
+      <c r="I35" s="9" cm="1">
         <f t="array" ref="I35">ABS(SUMPRODUCT((Q5:Q16/G35-ROUND(Q5:Q16/G35+0.5,0))^2))</f>
         <v>4.6905513541458124</v>
       </c>
-      <c r="J35" s="44" cm="1">
+      <c r="J35" s="28" cm="1">
         <f t="array" ref="J35">ABS(SUMPRODUCT((R5:R16/G35-ROUND(R5:R16/G35+0.5,0))^2))</f>
         <v>6.4419396283281332</v>
       </c>
     </row>
-    <row r="36" spans="7:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G36" s="53">
+    <row r="36" spans="7:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G36" s="37">
         <f>(1+15*0.7/25)*10^-19</f>
         <v>1.42E-19</v>
       </c>
-      <c r="H36" s="11" cm="1">
+      <c r="H36" s="9" cm="1">
         <f t="array" ref="H36">ABS(SUMPRODUCT((L5:L16/G36-ROUND(L5:L16/G36+0.5,0))^2))</f>
         <v>2.5107874114261617</v>
       </c>
-      <c r="I36" s="11" cm="1">
+      <c r="I36" s="9" cm="1">
         <f t="array" ref="I36">ABS(SUMPRODUCT((Q5:Q16/G36-ROUND(Q5:Q16/G36+0.5,0))^2))</f>
         <v>4.2048474936294307</v>
       </c>
-      <c r="J36" s="44" cm="1">
+      <c r="J36" s="28" cm="1">
         <f t="array" ref="J36">ABS(SUMPRODUCT((R5:R16/G36-ROUND(R5:R16/G36+0.5,0))^2))</f>
         <v>5.5206053090200129</v>
       </c>
     </row>
-    <row r="37" spans="7:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G37" s="53">
+    <row r="37" spans="7:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G37" s="61">
         <f>(1+16*0.7/25)*10^-19</f>
         <v>1.4479999999999999E-19</v>
       </c>
-      <c r="H37" s="11" cm="1">
+      <c r="H37" s="9" cm="1">
         <f t="array" ref="H37">ABS(SUMPRODUCT((L5:L16/G37-ROUND(L5:L16/G37+0.5,0))^2))</f>
         <v>4.4869235735973358</v>
       </c>
-      <c r="I37" s="11" cm="1">
+      <c r="I37" s="60" cm="1">
         <f t="array" ref="I37">ABS(SUMPRODUCT((Q5:Q16/G37-ROUND(Q5:Q16/G37+0.5,0))^2))</f>
         <v>1.9957766539867345</v>
       </c>
-      <c r="J37" s="44" cm="1">
+      <c r="J37" s="28" cm="1">
         <f t="array" ref="J37">ABS(SUMPRODUCT((R5:R16/G37-ROUND(R5:R16/G37+0.5,0))^2))</f>
         <v>4.0393646278240567</v>
       </c>
     </row>
-    <row r="38" spans="7:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G38" s="53">
+    <row r="38" spans="7:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G38" s="37">
         <f>(1+17*0.7/25)*10^-19</f>
         <v>1.4759999999999999E-19</v>
       </c>
-      <c r="H38" s="11" cm="1">
+      <c r="H38" s="9" cm="1">
         <f t="array" ref="H38">ABS(SUMPRODUCT((L5:L16/G38-ROUND(L5:L16/G38+0.5,0))^2))</f>
         <v>4.818038478499032</v>
       </c>
-      <c r="I38" s="11" cm="1">
+      <c r="I38" s="9" cm="1">
         <f t="array" ref="I38">ABS(SUMPRODUCT((Q5:Q16/G38-ROUND(Q5:Q16/G38+0.5,0))^2))</f>
         <v>3.7529847689025768</v>
       </c>
-      <c r="J38" s="44" cm="1">
+      <c r="J38" s="28" cm="1">
         <f t="array" ref="J38">ABS(SUMPRODUCT((R5:R16/G38-ROUND(R5:R16/G38+0.5,0))^2))</f>
         <v>5.3993588223788951</v>
       </c>
     </row>
-    <row r="39" spans="7:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G39" s="53">
+    <row r="39" spans="7:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G39" s="37">
         <f>(1+18*0.7/25)*10^-19</f>
         <v>1.5039999999999999E-19</v>
       </c>
-      <c r="H39" s="11" cm="1">
+      <c r="H39" s="9" cm="1">
         <f t="array" ref="H39">ABS(SUMPRODUCT((L5:L16/G39-ROUND(L5:L16/G39+0.5,0))^2))</f>
         <v>3.7257055673117296</v>
       </c>
-      <c r="I39" s="11" cm="1">
+      <c r="I39" s="9" cm="1">
         <f t="array" ref="I39">ABS(SUMPRODUCT((Q5:Q16/G39-ROUND(Q5:Q16/G39+0.5,0))^2))</f>
         <v>2.4891584476630295</v>
       </c>
-      <c r="J39" s="44" cm="1">
+      <c r="J39" s="28" cm="1">
         <f t="array" ref="J39">ABS(SUMPRODUCT((R5:R16/G39-ROUND(R5:R16/G39+0.5,0))^2))</f>
         <v>3.4102251568617419</v>
       </c>
     </row>
-    <row r="40" spans="7:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G40" s="53">
+    <row r="40" spans="7:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G40" s="37">
         <f>(1+19*0.7/25)*10^-19</f>
         <v>1.5320000000000001E-19</v>
       </c>
-      <c r="H40" s="11" cm="1">
+      <c r="H40" s="9" cm="1">
         <f t="array" ref="H40">ABS(SUMPRODUCT((L5:L16/G40-ROUND(L5:L16/G40+0.5,0))^2))</f>
         <v>4.5669715204620287</v>
       </c>
-      <c r="I40" s="11" cm="1">
+      <c r="I40" s="9" cm="1">
         <f t="array" ref="I40">ABS(SUMPRODUCT((Q5:Q16/G40-ROUND(Q5:Q16/G40+0.5,0))^2))</f>
         <v>3.6309702983981555</v>
       </c>
-      <c r="J40" s="44" cm="1">
+      <c r="J40" s="28" cm="1">
         <f t="array" ref="J40">ABS(SUMPRODUCT((R5:R16/G40-ROUND(R5:R16/G40+0.5,0))^2))</f>
         <v>3.4639336522009394</v>
       </c>
     </row>
-    <row r="41" spans="7:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G41" s="53">
+    <row r="41" spans="7:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G41" s="37">
         <f>(1+20*0.7/25)*10^-19</f>
         <v>1.56E-19</v>
       </c>
-      <c r="H41" s="11" cm="1">
+      <c r="H41" s="9" cm="1">
         <f t="array" ref="H41">ABS(SUMPRODUCT((L5:L16/G41-ROUND(L5:L16/G41+0.5,0))^2))</f>
         <v>4.0825130881842169</v>
       </c>
-      <c r="I41" s="11" cm="1">
+      <c r="I41" s="9" cm="1">
         <f t="array" ref="I41">ABS(SUMPRODUCT((Q5:Q16/G41-ROUND(Q5:Q16/G41+0.5,0))^2))</f>
         <v>2.6072536343234356</v>
       </c>
-      <c r="J41" s="44" cm="1">
+      <c r="J41" s="28" cm="1">
         <f t="array" ref="J41">ABS(SUMPRODUCT((R5:R16/G41-ROUND(R5:R16/G41+0.5,0))^2))</f>
         <v>6.9413376941656368</v>
       </c>
     </row>
-    <row r="42" spans="7:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G42" s="53">
+    <row r="42" spans="7:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G42" s="37">
         <f>(1+21*0.7/25)*10^-19</f>
         <v>1.588E-19</v>
       </c>
-      <c r="H42" s="11" cm="1">
+      <c r="H42" s="9" cm="1">
         <f t="array" ref="H42">ABS(SUMPRODUCT((L5:L16/G42-ROUND(L5:L16/G42+0.5,0))^2))</f>
         <v>3.663665936067444</v>
       </c>
-      <c r="I42" s="11" cm="1">
+      <c r="I42" s="9" cm="1">
         <f t="array" ref="I42">ABS(SUMPRODUCT((Q5:Q16/G42-ROUND(Q5:Q16/G42+0.5,0))^2))</f>
         <v>5.0349651044122501</v>
       </c>
-      <c r="J42" s="44" cm="1">
+      <c r="J42" s="28" cm="1">
         <f t="array" ref="J42">ABS(SUMPRODUCT((R5:R16/G42-ROUND(R5:R16/G42+0.5,0))^2))</f>
         <v>2.472251872932179</v>
       </c>
     </row>
-    <row r="43" spans="7:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G43" s="53">
+    <row r="43" spans="7:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G43" s="37">
         <f>(1+22*0.7/25)*10^-19</f>
         <v>1.616E-19</v>
       </c>
-      <c r="H43" s="11" cm="1">
+      <c r="H43" s="9" cm="1">
         <f t="array" ref="H43">ABS(SUMPRODUCT((L5:L16/G43-ROUND(L5:L16/G43+0.5,0))^2))</f>
         <v>3.561790786180512</v>
       </c>
-      <c r="I43" s="11" cm="1">
+      <c r="I43" s="9" cm="1">
         <f t="array" ref="I43">ABS(SUMPRODUCT((Q5:Q16/G43-ROUND(Q5:Q16/G43+0.5,0))^2))</f>
         <v>4.3708836289837718</v>
       </c>
-      <c r="J43" s="44" cm="1">
+      <c r="J43" s="28" cm="1">
         <f t="array" ref="J43">ABS(SUMPRODUCT((R5:R16/G43-ROUND(R5:R16/G43+0.5,0))^2))</f>
         <v>3.2952861496504608</v>
       </c>
     </row>
-    <row r="44" spans="7:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G44" s="53">
+    <row r="44" spans="7:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G44" s="37">
         <f>(1+23*0.7/25)*10^-19</f>
         <v>1.6439999999999999E-19</v>
       </c>
-      <c r="H44" s="11" cm="1">
+      <c r="H44" s="9" cm="1">
         <f t="array" ref="H44">ABS(SUMPRODUCT((L5:L16/G44-ROUND(L5:L16/G44+0.5,0))^2))</f>
         <v>3.5341810262779516</v>
       </c>
-      <c r="I44" s="11" cm="1">
+      <c r="I44" s="9" cm="1">
         <f t="array" ref="I44">ABS(SUMPRODUCT((Q5:Q16/G44-ROUND(Q5:Q16/G44+0.5,0))^2))</f>
         <v>4.9621603649377937</v>
       </c>
-      <c r="J44" s="44" cm="1">
+      <c r="J44" s="28" cm="1">
         <f t="array" ref="J44">ABS(SUMPRODUCT((R5:R16/G44-ROUND(R5:R16/G44+0.5,0))^2))</f>
         <v>2.9505575188793669</v>
       </c>
     </row>
-    <row r="45" spans="7:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G45" s="53">
+    <row r="45" spans="7:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G45" s="37">
         <f>(1+24*0.7/25)*10^-19</f>
         <v>1.6719999999999999E-19</v>
       </c>
-      <c r="H45" s="11" cm="1">
+      <c r="H45" s="9" cm="1">
         <f t="array" ref="H45">ABS(SUMPRODUCT((L5:L16/G45-ROUND(L5:L16/G45+0.5,0))^2))</f>
         <v>5.2677673916318968</v>
       </c>
-      <c r="I45" s="11" cm="1">
+      <c r="I45" s="9" cm="1">
         <f t="array" ref="I45">ABS(SUMPRODUCT((Q5:Q16/G45-ROUND(Q5:Q16/G45+0.5,0))^2))</f>
         <v>3.7718179872560871</v>
       </c>
-      <c r="J45" s="44" cm="1">
+      <c r="J45" s="28" cm="1">
         <f t="array" ref="J45">ABS(SUMPRODUCT((R5:R16/G45-ROUND(R5:R16/G45+0.5,0))^2))</f>
         <v>4.4655601221480623</v>
       </c>
     </row>
-    <row r="46" spans="7:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G46" s="54">
+    <row r="46" spans="7:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="G46" s="38">
         <f>(1+25*0.7/25)*10^-19</f>
         <v>1.6999999999999999E-19</v>
       </c>
-      <c r="H46" s="62" cm="1">
+      <c r="H46" s="44" cm="1">
         <f t="array" ref="H46">ABS(SUMPRODUCT((L5:L16/G46-ROUND(L5:L16/G46+0.5,0))^2))</f>
         <v>5.010073518879981</v>
       </c>
-      <c r="I46" s="62" cm="1">
+      <c r="I46" s="44" cm="1">
         <f t="array" ref="I46">ABS(SUMPRODUCT((Q5:Q16/G46-ROUND(Q5:Q16/G46+0.5,0))^2))</f>
         <v>3.4545738172467209</v>
       </c>
-      <c r="J46" s="47" cm="1">
+      <c r="J46" s="31" cm="1">
         <f t="array" ref="J46">ABS(SUMPRODUCT((R5:R16/G46-ROUND(R5:R16/G46+0.5,0))^2))</f>
         <v>4.7307205290468461</v>
+      </c>
+    </row>
+    <row r="49" spans="7:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G49" t="s">
+        <v>42</v>
+      </c>
+      <c r="H49">
+        <f>(1+11*0.7/25)*10^-19</f>
+        <v>1.3080000000000001E-19</v>
+      </c>
+    </row>
+    <row r="50" spans="7:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G50" t="s">
+        <v>43</v>
+      </c>
+      <c r="H50">
+        <f>(1+16*0.7/25)*10^-19</f>
+        <v>1.4479999999999999E-19</v>
+      </c>
+    </row>
+    <row r="51" spans="7:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G51" t="s">
+        <v>44</v>
+      </c>
+      <c r="H51">
+        <f>(H49+H50)/2</f>
+        <v>1.378E-19</v>
+      </c>
+    </row>
+    <row r="52" spans="7:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G52" t="s">
+        <v>45</v>
+      </c>
+      <c r="H52">
+        <f>(H50-H49)/2</f>
+        <v>6.9999999999999916E-21</v>
       </c>
     </row>
   </sheetData>
